--- a/resultados_llama3/eval_comparison.xlsx
+++ b/resultados_llama3/eval_comparison.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S48"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4203,6 +4203,574 @@
       </c>
       <c r="R48" s="3" t="inlineStr"/>
       <c r="S48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>30191707</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>3 - Urgente</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>ESI-3</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>exame físico e possivelmente imagem ou medicação para dor</t>
+        </is>
+      </c>
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" t="b">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="3" t="inlineStr">
+        <is>
+          <t>O paciente apresenta dor intensa na perna direita, com EVA 8/10, o que satisfez o critério de dor intensa no Ponto B, mas como não há outros sintomas graves ou sinais vitais alterados, a classificação mais adequada é ESI-3, considerando a necessidade de avaliação e possivelmente recursos para aliviar a dor.</t>
+        </is>
+      </c>
+      <c r="R49" s="3" t="inlineStr"/>
+      <c r="S49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>30193081</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>3 - Urgente</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>ESI-3</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Exame físico e possivelmente imagem (RX) para avaliar a lesão na extremidade inferior</t>
+        </is>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="b">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="3" t="inlineStr">
+        <is>
+          <t>Paciente apresenta dor significativa na extremidade inferior, mas está ambulando independentemente e não mostra sinais de distresse sistêmico agudo. A classificação ESI-3 se justifica devido à necessidade de avaliação e possivelmente intervenção para a lesão, mas não há indicação de emergência imediata.</t>
+        </is>
+      </c>
+      <c r="R50" s="3" t="inlineStr"/>
+      <c r="S50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>32258048</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>3 - Urgente</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>ESI-3</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>exame físico
+imagem (RX/TC/USG/RM)</t>
+        </is>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" t="b">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3" t="inlineStr">
+        <is>
+          <t>Paciente com dor abdominal no quadrante inferior esquerdo, intensidade 6/10, mas sinais vitais estáveis e hemodinamicamente estável. Não atende aos critérios de ESI-1 ou ESI-2, portanto, segue para o ponto D, onde a classificação é ESI-3 devido aos sinais vitais normais.</t>
+        </is>
+      </c>
+      <c r="R51" s="3" t="inlineStr"/>
+      <c r="S51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>35664211</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>3 - Urgente</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>ESI-3</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>RX
+exame físico detalhado</t>
+        </is>
+      </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="b">
+        <v>0</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3" t="inlineStr">
+        <is>
+          <t>Paciente de 55 anos com mecanismo de lesão potencialmente grave, mas sem dor ou alterações significativas nos sinais vitais. O paciente necessita de avaliação detalhada e possivelmente exames de imagem para descartar lesões internas ou fraturas.</t>
+        </is>
+      </c>
+      <c r="R52" s="3" t="inlineStr"/>
+      <c r="S52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>36327718</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>3 - Urgente</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>ESI-3</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>exame físico e anamnese mais detalhados para investigar tontura</t>
+        </is>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" t="b">
+        <v>0</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="N53" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>Paciente apresenta tontura sem dor no peito, falta de ar ou trauma recente. Sinais vitais estão dentro dos limites normais. Como não há critérios para ESI-1 ou ESI-2 e os sinais vitais não indicam perigo, o paciente é classificado como ESI-3 devido à necessidade de investigação adicional para a tontura.</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>necessidade de investigar causa da tontura
+considerar história médica e medicamentos</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>30022323</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3 - Urgente</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>ESI-3</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>exame físico
+labs</t>
+        </is>
+      </c>
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" t="b">
+        <v>0</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="3" t="inlineStr">
+        <is>
+          <t>Paciente apresenta dor abdominal com EVA 5/10, sem sinais de perigo imediato. Sinais vitais estão dentro dos limites normais. Portanto, a classificação é ESI-3, de acordo com o Ponto D do algoritmo ESI.</t>
+        </is>
+      </c>
+      <c r="R54" s="3" t="inlineStr"/>
+      <c r="S54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>30025651</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3 - Urgente</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>ESI-3</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>exame físico e possivelmente exame de urina</t>
+        </is>
+      </c>
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" t="b">
+        <v>0</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" s="3" t="inlineStr">
+        <is>
+          <t>A paciente apresenta dor pélvica e disúria, o que sugere uma possível infecção do trato urinário. No entanto, os sinais vitais estão dentro dos limites normais e a paciente não apresenta sinais de choque ou deterioração clínica. Portanto, a classificação é ESI-3, pois a paciente requer atenção médica, mas não é considerada emergente.</t>
+        </is>
+      </c>
+      <c r="R55" s="3" t="inlineStr"/>
+      <c r="S55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>30061072</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>3 - Urgente</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>ESI-3</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>exame físico e anamnese não são considerados recursos, mas podem ser necessários para o diagnóstico, portanto, considerando a necessidade de exames adicionais como um recurso</t>
+        </is>
+      </c>
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" t="b">
+        <v>0</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="3" t="inlineStr">
+        <is>
+          <t>O paciente apresenta dor abdominal de lado direito com uma pontuação de dor de 2, sinais vitais dentro dos parâmetros normais, o que não indica necessidade de intervenção imediata ou alta urgência. A classificação como ESI-3 se baseia na necessidade de avaliação e possíveis exames adicionais para determinar a causa da dor abdominal.</t>
+        </is>
+      </c>
+      <c r="R56" s="3" t="inlineStr"/>
+      <c r="S56" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4310,13 +4878,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>71.40000000000001</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="6">
@@ -4365,13 +4933,13 @@
       </c>
       <c r="B8" s="14" t="inlineStr"/>
       <c r="C8" s="14" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>59.6</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="9">
@@ -4463,7 +5031,7 @@
         <v>2</v>
       </c>
       <c r="D13" s="22" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E13" s="24" t="inlineStr"/>
       <c r="F13" s="24" t="inlineStr"/>
@@ -4589,13 +5157,13 @@
         <v>2</v>
       </c>
       <c r="D20" s="28" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E20" s="24" t="inlineStr"/>
       <c r="F20" s="24" t="inlineStr"/>
       <c r="G20" s="24" t="inlineStr"/>
       <c r="H20" s="25" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
